--- a/docs/Mapping_casi_uso/nascita/Dic_Nasc_998_2.xlsx
+++ b/docs/Mapping_casi_uso/nascita/Dic_Nasc_998_2.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="87">
   <si>
     <t>Sezione</t>
   </si>
@@ -129,12 +129,6 @@
   </si>
   <si>
     <t>idAttoCartaceo</t>
-  </si>
-  <si>
-    <t>Atto secretato</t>
-  </si>
-  <si>
-    <t>flagsecretato</t>
   </si>
   <si>
     <t>Ente dichiarante</t>
@@ -337,7 +331,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.171875" customWidth="true" bestFit="true"/>
@@ -673,19 +667,19 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>10</v>
@@ -696,16 +690,16 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>43</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>44</v>
@@ -719,16 +713,16 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>46</v>
@@ -742,16 +736,16 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>47</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>48</v>
@@ -765,7 +759,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>49</v>
@@ -774,7 +768,7 @@
         <v>13</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>50</v>
@@ -788,16 +782,16 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>52</v>
@@ -811,7 +805,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>53</v>
@@ -820,7 +814,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>54</v>
@@ -834,7 +828,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>55</v>
@@ -843,7 +837,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>56</v>
@@ -857,7 +851,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>57</v>
@@ -866,7 +860,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>58</v>
@@ -880,7 +874,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>59</v>
@@ -889,7 +883,7 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>60</v>
@@ -903,7 +897,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>61</v>
@@ -912,7 +906,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>62</v>
@@ -926,7 +920,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>63</v>
@@ -935,7 +929,7 @@
         <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>64</v>
@@ -949,19 +943,19 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>10</v>
@@ -972,16 +966,16 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" s="2" t="s">
         <v>67</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>69</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>70</v>
@@ -995,7 +989,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>71</v>
@@ -1004,7 +998,7 @@
         <v>13</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>72</v>
@@ -1018,7 +1012,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>73</v>
@@ -1027,7 +1021,7 @@
         <v>13</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>74</v>
@@ -1041,7 +1035,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>75</v>
@@ -1050,7 +1044,7 @@
         <v>13</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>76</v>
@@ -1064,7 +1058,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>77</v>
@@ -1073,10 +1067,10 @@
         <v>13</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>78</v>
+        <v>18</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>10</v>
@@ -1087,19 +1081,19 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="E33" s="2" t="s">
         <v>79</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>10</v>
@@ -1110,7 +1104,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>80</v>
@@ -1119,10 +1113,10 @@
         <v>13</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>10</v>
@@ -1133,19 +1127,19 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="E35" s="2" t="s">
         <v>82</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>10</v>
@@ -1156,7 +1150,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>83</v>
@@ -1165,7 +1159,7 @@
         <v>13</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>69</v>
+        <v>17</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>84</v>
@@ -1179,13 +1173,13 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>85</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>17</v>
@@ -1197,29 +1191,6 @@
         <v>10</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G38" s="2" t="s">
         <v>19</v>
       </c>
     </row>
